--- a/feature/replace-image-diagrams-by-plantuml/ig/ValueSet-sas-valueset-appointmentreason.xlsx
+++ b/feature/replace-image-diagrams-by-plantuml/ig/ValueSet-sas-valueset-appointmentreason.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T13:42:16+00:00</t>
+    <t>2024-07-17T14:09:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
